--- a/hira_material_automation/output/monthly/202601_202604__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202604__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-04T21:38:03</t>
+          <t>2026-04-14T21:56:02</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>b7e2b364d149beb2fb9676e56901a086fa49f1f96d6b63fb400cbb2a07e8a806</t>
+          <t>9191c02f7dee25cedede361d4d7fe6ec49ef7f9d07810bbad958cfa16b5b6cd8</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202604__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202604__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-14T21:56:02</t>
+          <t>2026-04-24T21:54:17</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9191c02f7dee25cedede361d4d7fe6ec49ef7f9d07810bbad958cfa16b5b6cd8</t>
+          <t>1c3ea31df8fa75cab26ed925e938f7819879e40f6475a11b3d7137d3cbf5a0ab</t>
         </is>
       </c>
     </row>
